--- a/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0002T0006Z000C1N37_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0002T0006Z000C1N37_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>36.31525752197807</v>
+        <v>5.901229347321436</v>
       </c>
       <c r="D2" t="n">
-        <v>35.92428689172108</v>
+        <v>5.837696619904676</v>
       </c>
       <c r="E2" t="n">
-        <v>14.69243543345038</v>
+        <v>2.387520757935687</v>
       </c>
       <c r="F2" t="n">
-        <v>19.88802336492846</v>
+        <v>3.231803796800875</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>32.31303802750138</v>
+        <v>5.250868679468975</v>
       </c>
       <c r="D3" t="n">
-        <v>33.69324812845868</v>
+        <v>5.475152820874535</v>
       </c>
       <c r="E3" t="n">
-        <v>14.69243543345038</v>
+        <v>2.387520757935687</v>
       </c>
       <c r="F3" t="n">
-        <v>19.88802336492846</v>
+        <v>3.231803796800875</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>30.24606501594311</v>
+        <v>4.914985565090755</v>
       </c>
       <c r="D4" t="n">
-        <v>11.71537451385998</v>
+        <v>1.903748358502247</v>
       </c>
       <c r="E4" t="n">
-        <v>14.69243543345038</v>
+        <v>2.387520757935687</v>
       </c>
       <c r="F4" t="n">
-        <v>19.88802336492846</v>
+        <v>3.231803796800875</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>56.09902245119045</v>
+        <v>9.116091148318448</v>
       </c>
       <c r="D5" t="n">
-        <v>57.4528471668356</v>
+        <v>9.336087664610785</v>
       </c>
       <c r="E5" t="n">
-        <v>14.69243543345038</v>
+        <v>2.387520757935687</v>
       </c>
       <c r="F5" t="n">
-        <v>19.88802336492846</v>
+        <v>3.231803796800875</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>67.4372155557293</v>
+        <v>10.95854752780601</v>
       </c>
       <c r="D6" t="n">
-        <v>68.77667404233071</v>
+        <v>11.17620953187874</v>
       </c>
       <c r="E6" t="n">
-        <v>14.69243543345038</v>
+        <v>2.387520757935687</v>
       </c>
       <c r="F6" t="n">
-        <v>19.88802336492846</v>
+        <v>3.231803796800875</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
